--- a/docs/compliance/spreadsheets/ROPA.xlsx
+++ b/docs/compliance/spreadsheets/ROPA.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Article 30 record" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retention decision" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Read me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Article 30 record" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Retention decision" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Article 30 record'!$A$1:$O$8</definedName>
@@ -509,7 +509,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Last reviewed: 2026-08-25</t>
+          <t>Last reviewed: 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
-          <t>Row-level security (ENABLE and FORCE) on 82 of 88 tables, 197 policies; audit by trigger; DELETE revoked</t>
+          <t>Row-level security (ENABLE and FORCE) on 83 of 89 tables, 205 policies; audit by trigger; DELETE revoked; permissions checked per branch</t>
         </is>
       </c>
       <c r="N2" s="6" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Principal id, table, row id, action, timestamp, before/after values — which include personal data wherever the audited row did</t>
+          <t>Principal id, table, row id, operation, timestamp, client IP address, before/after values — which include personal data wherever the audited row did</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>NOT SET. NFR-10 requires 12 months minimum, searchable and exportable — neither the search nor the export is built</t>
+          <t>NOT SET. NFR-10 requires 12 months minimum, searchable and exportable — the search and the CSV export are built; the period is not</t>
         </is>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>Insert-only. DELETE revoked. 80 triggers attached by a loop rather than a list</t>
+          <t>Insert-only. DELETE revoked. 81 triggers; the build fails for any business table without one</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>Granted by the customer, time-boxed, revocable, read-only by structure (SELECT policies only), logged once per transaction inside that transaction</t>
+          <t>Granted by the customer, time-boxed, revocable, read-only unless the customer grants write scope (updates only, never inserts or deletes), logged once per transaction inside that transaction</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">

--- a/docs/compliance/spreadsheets/ROPA.xlsx
+++ b/docs/compliance/spreadsheets/ROPA.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
-          <t>Row-level security (ENABLE and FORCE) on 83 of 89 tables, 205 policies; audit by trigger; DELETE revoked; permissions checked per branch</t>
+          <t>Row-level security (ENABLE and FORCE) on 87 of 93 tables, 211 policies; audit by trigger; DELETE revoked; permissions checked per branch</t>
         </is>
       </c>
       <c r="N2" s="6" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>Insert-only. DELETE revoked. 81 triggers; the build fails for any business table without one</t>
+          <t>Insert-only. DELETE revoked. 85 triggers; the build fails for any business table without one</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Turning emailed enquiries into structured records</t>
+          <t>Turning emailed and WhatsApp enquiries into structured records, and — where a branch switches the intake agent on — answering the sender with at most one confirmation and a capped number of clarifications</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Anyone who emails the enquiry mailbox</t>
+          <t>Anyone who emails the enquiry mailbox or messages a business WhatsApp number</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>mailboxes, messages, message_attachments</t>
+          <t>mailboxes, whatsapp_numbers, messages, message_attachments, intake_conversations, intake_turns</t>
         </is>
       </c>
       <c r="O6" s="6" t="inlineStr">
         <is>
-          <t>Live. The mailbox is on the open internet</t>
+          <t>Live. The mailbox is on the open internet. The intake agent ships off per branch</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Enquiry and document text, which may contain any of the categories above</t>
+          <t>Enquiry and document text — for the intake agent, every customer message in the conversation and any PDF or image attached to it — which may contain any of the categories above</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">

--- a/docs/compliance/spreadsheets/ROPA.xlsx
+++ b/docs/compliance/spreadsheets/ROPA.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Sender address, message body, attachments — uncontrolled, because anyone may write in</t>
+          <t>Sender address or phone number, message body, attachments (WhatsApp media fetched through Kapso), and staff WhatsApp replies sent from outside the product — uncontrolled, because anyone may write in</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
